--- a/data/math_data.xlsx
+++ b/data/math_data.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目次_数学2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目次_数学1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目次_数学2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -115,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -147,6 +148,7 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -512,6 +514,403 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>編</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>章番号</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>章タイトル</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>節番号</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>節タイトル</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>小節番号</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>小節タイトル</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>ページ</t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>算数から数学へ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0章</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>算数から数学へ</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>算数から数学へ</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>正負の数</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1章</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>数の世界をひろげよう</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>数の世界をひろげよう</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>文字と式</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2章</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>数学のことばを身につけよう</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>数学のことばを身につけよう</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>方程式</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3章</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>未知の数の求め方を考えよう</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>未知の数の求め方を考えよう</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>比例と反比例</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4章</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>数量の関係を調べて問題を解決しよう</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>数量の関係を調べて問題を解決しよう</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>平面図形</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5章</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>平面図形の見方をひろげよう</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>平面図形の見方をひろげよう</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>空間図形</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>6章</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>立体の見方をひろげよう</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>立体の見方をひろげよう</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>データの分析と活用</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7章</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>データを活用して判断しよう</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>データを活用して判断しよう</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>225</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>★試験範囲(1年) P225-248</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>巻末</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>数学の目でふり返ろう</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>数学の目でふり返ろう</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>巻末</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>学びのベース</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>算数 まとめ編</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>巻末</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>学びのベース</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>算数 たしかめ編</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>巻末</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1年のふり返り</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1年のふり返り</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>巻末</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>補充の問題</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>補充の問題</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>巻末</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>数学の自由研究</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>数学の自由研究</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>281</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
